--- a/precios.xlsx
+++ b/precios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fer\Python\Monitor de stocks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4986480F-61A3-4A0C-8859-B760D3DADE50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFEFFD32-BD07-4E04-8A7B-B9C912DF081A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>symbol</t>
   </si>
@@ -31,22 +31,19 @@
     <t>time</t>
   </si>
   <si>
-    <t>BINANCE:BTCUSDT</t>
-  </si>
-  <si>
-    <t>BINANCE:ETHUSDT</t>
-  </si>
-  <si>
-    <t>BINANCE:SOLUSDT</t>
-  </si>
-  <si>
-    <t>112662.83</t>
-  </si>
-  <si>
-    <t>3984.95</t>
-  </si>
-  <si>
-    <t>194.35</t>
+    <t>FLS</t>
+  </si>
+  <si>
+    <t>TER</t>
+  </si>
+  <si>
+    <t>STX</t>
+  </si>
+  <si>
+    <t>MIR</t>
+  </si>
+  <si>
+    <t>BE</t>
   </si>
 </sst>
 </file>
@@ -411,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
@@ -434,33 +431,55 @@
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
+      <c r="B2">
+        <v>68.95</v>
       </c>
       <c r="C2" s="2">
-        <v>45959.026400462964</v>
+        <v>45959.889270833337</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
+      <c r="B3">
+        <v>173.91</v>
       </c>
       <c r="C3" s="2">
-        <v>45959.026400462964</v>
+        <v>45959.889270833337</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
-        <v>8</v>
+      <c r="B4">
+        <v>265.54000000000002</v>
       </c>
       <c r="C4" s="2">
-        <v>45959.026400462964</v>
+        <v>45959.889270833337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>29.75</v>
+      </c>
+      <c r="C5" s="2">
+        <v>45959.889270833337</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6">
+        <v>133.71</v>
+      </c>
+      <c r="C6" s="2">
+        <v>45959.889270833337</v>
       </c>
     </row>
   </sheetData>
